--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -663,19 +663,19 @@
         <v>16</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.09</v>
+        <v>0.07</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
@@ -689,16 +689,16 @@
         <v>0.48</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="10">
@@ -712,13 +712,13 @@
         <v>-0.54</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.48</v>
@@ -735,16 +735,16 @@
         <v>-0.66</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="12">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:37</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2018_coquimbo.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
